--- a/data_extactor/batch_10_fa/batch_0042_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0042_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Adobe Photoshop | Adobe Illustrator | Adobe InDesign | Adobe Acrobat | نرم‌افزار گرافیک | Microsoft Word | Microsoft Excel | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | Microsoft PowerPoint | نرم‌افزار ویرایش گرافیک | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Windows | سیستم مدیریت نگهداری کامپیوتری CMMS</t>
+          <t>Adobe Photoshop | Adobe Illustrator | Adobe InDesign | Adobe Acrobat | نرم‌افزار گرافیکی | Microsoft Word | Microsoft Excel | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | Microsoft PowerPoint | نرم‌افزار ویرایش گرافیکی | نرم‌افزار Microsoft Office | Microsoft Windows | سیستم مدیریت نگهداری کامپیوتری CMMS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | صحبت کردن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مخابرات | کامپیوتر و الکترونیک | ارتباطات و رسانه | زبان انگلیسی | مهندسی و فناوری | هنرهای زیبا | خدمات مشتری و شخصی</t>
+          <t>مخابرات | رایانه و الکترونیک | ارتباطات و رسانه | زبان انگلیسی | مهندسی و فناوری | هنرهای زیبا | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | نظم‌دهی اطلاعات | دید نزدیک | تجسم | ثبات بازو-دست | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند اندامی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | دید دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای تهویه مطبوع | صرف زمان برای نشستن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | محیط داخلی، بدون تهویه مطبوع | فشار زمانی | اهمیت دقیق یا صحیح بودن | پیامد خطا | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | صرف زمان برای بالا رفتن از نردبان، داربست یا دکل | قرار گرفتن در معرض تجهیزات خطرناک</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | محیط داخلی، بدون کنترل شرایط محیطی | فشار زمانی | اهمیت دقیق یا درست بودن | پیامد خطا | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرار گرفتن در معرض تجهیزات خطرناک</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنسین‌های صوتی و تصویری | تکنسین‌های پخش | تکنسین‌های مهندسی صدا | تکنسین‌های نورپردازی | اپراتورهای دوربین، تلویزیون، ویدیو و فیلم | تدوین‌گران فیلم و ویدیو | عکاسان | مدیران/کارگردانان فنی رسانه | تهیه‌کنندگان و کارگردانان | نصاب‌ها و تعمیرکاران تجهیزات مخابراتی، به جز نصاب‌های خط | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | نصاب‌ها و تعمیرکاران تجهیزات رادیویی، سلولی و دکل | متخصصان پشتیبانی کاربر کامپیوتر | هنرمندان جلوه‌های ویژه و انیماتورها | طراحان صحنه و نمایشگاه | مدیران برنامه‌ریزی رسانه | نصاب‌ها و تعمیرکاران تجهیزات سمعی و بصری | برق‌کاران | مهندسان ثابت و اپراتورهای دیگ بخار | کارکنان رسانه و ارتباطات، سایر</t>
+          <t>تکنسین‌های صوتی و تصویری | تکنسین‌های پخش | تکنسین‌های مهندسی صدا | تکنسین‌های نورپردازی | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | تدوینگران فیلم و ویدئو | عکاسان | مدیران/کارگردانان فنی رسانه | تهیه‌کنندگان و کارگردانان | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | نصابان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل | متخصصان پشتیبانی کاربران کامپیوتر | هنرمندان جلوه‌های ویژه و انیماتورها | طراحان صحنه و نمایشگاه | مدیران برنامه‌ریزی رسانه | نصب‌کنندگان و تعمیرکنندگان تجهیزات صوتی و تصویری | برق‌کاران | مهندسان تاسیسات و اپراتورهای دیگ بخار | کارکنان رسانه و ارتباطات، سایر</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ACOM Solutions RAPID EMR | Acrendo A.I.med | Addison Health Systems WritePad EHR | Advantage Software Chiropractic Advantage | نرم‌افزار صورت‌حساب | BioEx Systems Exercise Pro | ChiroSoft | ChiroTouch EHR | DataCom Software Business Products M.I.S. Clinic | DocumentPlus | E-Z BIS Office | نرم‌افزار صورت‌حساب پزشکی EZClaim | EZnotes | Electro Meridian Imaging EMI | نرم‌افزار پرونده الکترونیک سلامت EMR | ForteEMR | GalacTek ECLIPSE | InPhase Technologies Group InPhase Concept | Life Systems Software ChiroSuite EHR | MRX Solutions OfficeMaster | MicroFour PracticeStudio.NET EMR | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | PPT4Drs Quixote | نرم‌افزار مدیریت مطب PMS | PracticePRO Software Systems QuickPractice | Pulse Software ChiroPulse 365 | Quick Notes QNotes Office EMR | نرم‌افزار زمان‌بندی | Software Motif MyEMR | Softworx Solutions ChiroWrite | Versatile Software Systems VersaSoft Chiro</t>
+          <t>ACOM Solutions RAPID EMR | Acrendo A.I.med | Addison Health Systems WritePad EHR | Advantage Software Chiropractic Advantage | نرم‌افزار صدور صورتحساب | BioEx Systems Exercise Pro | ChiroSoft | ChiroTouch EHR | DataCom Software Business Products M.I.S. Clinic | DocumentPlus | E-Z BIS Office | نرم‌افزار صورت‌حساب پزشکی EZClaim | EZnotes | Electro Meridian Imaging EMI | نرم‌افزار پرونده الکترونیک سلامت EMR | ForteEMR | GalacTek ECLIPSE | InPhase Technologies Group InPhase Concept | Life Systems Software ChiroSuite EHR | MRX Solutions OfficeMaster | MicroFour PracticeStudio.NET EMR | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | PPT4Drs Quixote | نرم‌افزار مدیریت مطب PMS | PracticePRO Software Systems QuickPractice | Pulse Software ChiroPulse 365 | Quick Notes QNotes Office EMR | نرم‌افزار زمان‌بندی | Software Motif MyEMR | Softworx Solutions ChiroWrite | Versatile Software Systems VersaSoft Chiro</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب | صحبت کردن | تفکر انتقادی | نوشتن | علوم | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | علوم | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زبان انگلیسی | خدمات مشتری و شخصی | زیست‌شناسی | روان‌شناسی | مدیریت و اداره | اداری | پرسنل و منابع انسانی | آموزش و پرورش | درمان و مشاوره | فروش و بازاریابی | کامپیوتر و الکترونیک</t>
+          <t>پزشکی و دندان‌پزشکی | زبان انگلیسی | خدمات مشتری و شخصی | زیست‌شناسی | روان‌شناسی | مدیریت و اداره | اداری | پرسنل و منابع انسانی | آموزش و پرورش | درمان و مشاوره | فروش و بازاریابی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان نوشتاری | نظم‌دهی اطلاعات | وضوح گفتار | دید نزدیک | تشخیص گفتار | قدرت تنه | هماهنگی چند اندامی | ثبات بازو-دست | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | مهارت انگشتان | روانی ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | ترتیب‌دهی اطلاعات | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | قدرت تنه | هماهنگی چند عضو | ثبات دست و بازو | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | مهارت انگشتان | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>تماس با دیگران | بحث‌های حضوری با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای تهویه مطبوع | مجاورت فیزیکی | مکالمات تلفنی | اهمیت دقیق یا صحیح بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | ایمیل | اهمیت تکرار وظایف مشابه | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نامه‌ها و یادداشت‌های کتبی | کار با یا مشارکت در یک گروه کاری یا تیم | نتایج کاری و خروجی‌های سایر کارکنان | صرف زمان برای انجام حرکات تکراری | پیامد خطا | برخورد با مشتریان خارجی یا عموم مردم | فشار زمانی | صرف زمان برای ایستادن | سلامت و ایمنی سایر کارکنان</t>
+          <t>ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | نزدیکی فیزیکی | مکالمات تلفنی | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | ایمیل | اهمیت تکرار وظایف یکسان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نامه‌ها و یادداشت‌های کتبی | کار با یا مشارکت در یک گروه کاری یا تیم | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای انجام حرکات تکراری | پیامد خطا | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی | صرف زمان برای ایستادن | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>متخصصان طب سوزنی | متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیهوشی | متخصصان قلب | متخصصان پوست | پزشکان طب اورژانس | پزشکان طب خانواده | پزشکان داخلی عمومی | پزشکان طب طبیعی | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | چشم‌پزشکان، به جز کودکان | اپتومتریست‌ها | جراحان ارتوپد، به جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | روان‌پزشکان | متخصصان اورولوژی</t>
+          <t>طب‌سوزنی‌ها | متخصصان آلرژی و ایمونولوژی | متخصصان بیهوشی | متخصصان قلب | متخصصان پوست | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | پزشکان ناتوروپاتی | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | چشم‌پزشکان، به‌جز کودکان | اپتومتریست‌ها | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | روان‌پزشکان | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ABELSoft ABELDent | ACE Dental | AlphaDent | AltaPoint Data Systems AltaPoint Dental | DSN Software Dental-Exec | DSN Software Oral Surgery-Exec | DSN Software Perio-Exec | Data Team DDS | نرم‌افزار نمودار دندانپزشکی | نرم‌افزار سوابق بالینی دندانپزشکی | نرم‌افزار رادیولوژی دیجیتال دندانپزشکی | نرم‌افزار تصویربرداری دندانپزشکی | نرم‌افزار تصویربرداری داخل دهانی دندانپزشکی | DentiMax | EZ 2000 | Genesis Dental | Henry Schein DentalVision Professional | Henry Schein Dentrix | Henry Schein Easy Dental | Henry Schein EndoVision | Henry Schein PerioVision | Kodak Dental Systems Kodak PRACTICEWORKS نرم‌افزار مدیریت مطب PMS | Kodak Dental Systems Kodak SOFTDENT نرم‌افزار مدیریت مطب PMS | MDC Services DentalMate | MOGO Dental Software MOGO | Microsoft Excel | نرم‌افزار Microsoft Office | OCS Office-Partner | Open Dental | PEB XLDent | Patterson Dental Supply Patterson EagleSoft | نرم‌افزار مدیریت مطب PMS | Teleo Practice Services The Complete Practitioner | نرم‌افزار ToothPics | نرم‌افزار نمودار پریو فعال‌شونده با صدا | نرم‌افزار مرورگر وب | Windent OMS | Windent SQL | نرم‌افزار پرونده الکترونیک سلامت eClinicalWorks</t>
+          <t>ABELSoft ABELDent | ACE Dental | AlphaDent | AltaPoint Data Systems AltaPoint Dental | DSN Software Dental-Exec | DSN Software Oral Surgery-Exec | DSN Software Perio-Exec | Data Team DDS | نرم‌افزار نمودار دندانپزشکی | نرم‌افزار سوابق بالینی دندانپزشکی | نرم‌افزار رادیولوژی دیجیتال دندانپزشکی | نرم‌افزار تصویربرداری دندانپزشکی | نرم‌افزار تصویربرداری داخل دهانی دندانپزشکی | DentiMax | EZ 2000 | Genesis Dental | Henry Schein DentalVision Professional | Henry Schein Dentrix | Henry Schein Easy Dental | Henry Schein EndoVision | Henry Schein PerioVision | Kodak Dental Systems Kodak PRACTICEWORKS نرم‌افزار مدیریت مطب PMS | Kodak Dental Systems Kodak SOFTDENT Practice management software PMS | MDC Services DentalMate | MOGO Dental Software MOGO | Microsoft Excel | نرم‌افزار Microsoft Office | OCS Office-Partner | Open Dental | PEB XLDent | Patterson Dental Supply Patterson EagleSoft | نرم‌افزار مدیریت مطب PMS | Teleo Practice Services The Complete Practitioner | نرم‌افزار ToothPics | نرم‌افزار نمودار پریو فعال‌شونده با صدا | نرم‌افزار مرورگر وب | Windent OMS | Windent SQL | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | صحبت کردن | گوش دادن فعال | درک مطلب | یادگیری فعال | علوم | نوشتن | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال | درک مطلب | یادگیری فعال | علوم | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتری و شخصی | زبان انگلیسی | زیست‌شناسی | روان‌شناسی | آموزش و پرورش | مدیریت و اداره | پرسنل و منابع انسانی | اقتصاد و حسابداری</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زبان انگلیسی | زیست‌شناسی | روان‌شناسی | آموزش و پرورش | مدیریت و اداره | پرسنل و منابع انسانی | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>مهارت انگشتان | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ثبات بازو-دست | دید نزدیک | درک شنیداری | درک نوشتاری | بیان شفاهی | دقت کنترل | وضوح گفتار | نظم‌دهی اطلاعات | توجه انتخابی | مهارت دستی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | هماهنگی چند اندامی | انعطاف‌پذیری بستار | بیان نوشتاری | تجسم | روانی ایده‌ها | خلاقیت | تشخیص رنگ بصری | درک عمق | سرعت ادراکی | توانایی عددی | استدلال ریاضی</t>
+          <t>مهارت انگشتان | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ثبات دست و بازو | بینایی نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | دقت کنترل | وضوح گفتار | ترتیب‌دهی اطلاعات | توجه انتخابی | مهارت دستی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | هماهنگی چند عضو | انعطاف‌پذیری بستار | بیان کتبی | تجسم | روانی ایده‌ها | اصالت | تشخیص رنگ بصری | درک عمق | سرعت ادراکی | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | مجاورت فیزیکی | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا صحیح بودن | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض بیماری یا عفونت | نتایج کاری و خروجی‌های سایر کارکنان | تماس با دیگران | محیط داخلی، دارای تهویه مطبوع | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای انجام حرکات تکراری | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | برخورد با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض تابش | صرف زمان برای نشستن | اهمیت تکرار وظایف مشابه | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | ایمیل | قرار گرفتن در معرض آلاینده‌ها | سطح رقابت | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای خم شدن یا چرخاندن بدن | موقعیت‌های تعارض</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | پیامدهای کاری و نتایج سایر کارکنان | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای انجام حرکات تکراری | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض تابش | صرف زمان برای نشستن | اهمیت تکرار وظایف یکسان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | ایمیل | قرار گرفتن در معرض آلاینده‌ها | سطح رقابت | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای خم کردن یا چرخاندن بدن | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>متخصصان بیهوشی | متخصصان قلب | کایروپراکتورها | دستیاران دندانپزشک | بهداشت‌کاران دهان و دندان | متخصصان پوست | پزشکان طب اورژانس | پزشکان داخلی عمومی | دستیاران پزشکی | چشم‌پزشکان، به جز کودکان | اپتومتریست‌ها | جراحان دهان و فک و صورت | متخصصان ارتودنسی | جراحان ارتوپد، به جز کودکان | جراحان کودکان | پزشکان طب فیزیکی و توانبخشی | متخصصان پا (پودیاتریست‌ها) | متخصصان پروتز دندان | دستیاران جراحی | متخصصان اورولوژی</t>
+          <t>متخصصان بیهوشی | متخصصان قلب | کایروپراکتورها | دستیاران دندان‌پزشکی | بهداشت‌کاران دهان و دندان | متخصصان پوست | پزشکان طب اورژانس | پزشکان داخلی عمومی | دستیاران پزشکی | چشم‌پزشکان، به‌جز کودکان | اپتومتریست‌ها | جراحان دهان و فک و صورت | متخصصان ارتودنسی | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | پزشکان طب فیزیکی و توانبخشی | پزشکان پا | متخصصان پروتز دندان | دستیاران جراحی | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | صحبت کردن | یادگیری فعال | نظارت | نوشتن | علوم</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نظارت | نگارش | علوم</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی | آموزش و پرورش | شیمی | مدیریت و اداره | پرسنل و منابع انسانی | درمان و مشاوره | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی | آموزش و پرورش | شیمی | مدیریت و اداره | پرسنل و منابع انسانی | درمان و مشاوره | ریاضیات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ثبات بازو-دست | مهارت انگشتان | دید نزدیک | درک شنیداری | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | دقت کنترل | درک نوشتاری | نظم‌دهی اطلاعات | مهارت دستی | وضوح گفتار | تشخیص گفتار | بیان نوشتاری | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | هماهنگی چند اندامی | تشخیص رنگ بصری | تجسم | خلاقیت | سرعت ادراکی | روانی ایده‌ها</t>
+          <t>ثبات دست و بازو | مهارت انگشتان | بینایی نزدیک | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | دقت کنترل | درک کتبی | ترتیب‌دهی اطلاعات | مهارت دستی | وضوح گفتار | تشخیص گفتار | بیان کتبی | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | هماهنگی چند عضو | تشخیص رنگ بصری | تجسم | اصالت | سرعت ادراکی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض بیماری یا عفونت | مجاورت فیزیکی | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | تماس با دیگران | اهمیت دقیق یا صحیح بودن | فراوانی تصمیم‌گیری | نتایج کاری و خروجی‌های سایر کارکنان | محیط داخلی، دارای تهویه مطبوع | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | برخورد با مشتریان خارجی یا عموم مردم | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | پیامد خطا | ایمیل | سطح رقابت | فشار زمانی | موقعیت‌های تعارض</t>
+          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | پیامد خطا | ایمیل | سطح رقابت | فشار زمانی | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متخصصان بیهوشی | متخصصان قلب | دستیاران دندانپزشک | بهداشت‌کاران دهان و دندان | دندانپزشکان، عمومی | متخصصان پوست | پزشکان طب اورژانس | پزشکان داخلی عمومی | متخصصان مغز و اعصاب | متخصصان زنان و زایمان | چشم‌پزشکان، به جز کودکان | اپتومتریست‌ها | متخصصان ارتودنسی | جراحان ارتوپد، به جز کودکان | جراحان کودکان | پزشکان طب فیزیکی و توانبخشی | متخصصان پا (پودیاتریست‌ها) | متخصصان پروتز دندان | دستیاران جراحی | متخصصان اورولوژی</t>
+          <t>متخصصان بیهوشی | متخصصان قلب | دستیاران دندان‌پزشکی | بهداشت‌کاران دهان و دندان | دندانپزشکان، عمومی | متخصصان پوست | پزشکان طب اورژانس | پزشکان داخلی عمومی | متخصصان مغز و اعصاب | متخصصان زنان و زایمان | چشم‌پزشکان، به‌جز کودکان | اپتومتریست‌ها | متخصصان ارتودنسی | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | پزشکان طب فیزیکی و توانبخشی | پزشکان پا | متخصصان پروتز دندان | دستیاران جراحی | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | گوش دادن فعال | صحبت کردن | درک مطلب | یادگیری فعال | نوشتن | علوم | استراتژی‌های یادگیری</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | یادگیری فعال | نگارش | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتری و شخصی | زبان انگلیسی | زیست‌شناسی | کامپیوتر و الکترونیک | ریاضیات | مدیریت و اداره | آموزش و پرورش | فیزیک | مهندسی و فناوری</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زبان انگلیسی | زیست‌شناسی | رایانه و الکترونیک | ریاضیات | مدیریت و اداره | آموزش و پرورش | فیزیک | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | ثبات بازو-دست | مهارت انگشتان | دید نزدیک | تشخیص گفتار | وضوح گفتار | نظم‌دهی اطلاعات | مهارت دستی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | دقت کنترل | روانی ایده‌ها | تجسم | دید دور | اشتراک زمانی | خلاقیت</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ثبات دست و بازو | مهارت انگشتان | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | مهارت دستی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | دقت کنترل | روانی ایده‌ها | تجسم | بینایی دور | تقسیم توجه | اصالت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های حضوری با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تماس با دیگران | نتایج کاری و خروجی‌های سایر کارکنان | مجاورت فیزیکی | اهمیت دقیق یا صحیح بودن | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | محیط داخلی، دارای تهویه مطبوع | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ایمیل | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | مکالمات تلفنی | سطح رقابت | قرار گرفتن در معرض بیماری یا عفونت | اهمیت تکرار وظایف مشابه | قرار گرفتن در معرض تابش</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ایمیل | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | مکالمات تلفنی | سطح رقابت | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض تابش</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان قلب | کایروپراکتورها | دستیاران دندانپزشک | بهداشت‌کاران دهان و دندان | دندانپزشکان، عمومی | متخصصان پوست | پزشکان طب اورژانس | پزشکان داخلی عمومی | متخصصان مغز و اعصاب | متخصصان زنان و زایمان | چشم‌پزشکان، به جز کودکان | اپتومتریست‌ها | جراحان دهان و فک و صورت | جراحان ارتوپد، به جز کودکان | جراحان کودکان | پزشکان طب فیزیکی و توانبخشی | متخصصان پا (پودیاتریست‌ها) | متخصصان پروتز دندان | متخصصان اورولوژی</t>
+          <t>متخصصان آلرژی و ایمونولوژی | متخصصان قلب | کایروپراکتورها | دستیاران دندان‌پزشکی | بهداشت‌کاران دهان و دندان | دندانپزشکان، عمومی | متخصصان پوست | پزشکان طب اورژانس | پزشکان داخلی عمومی | متخصصان مغز و اعصاب | متخصصان زنان و زایمان | چشم‌پزشکان، به‌جز کودکان | اپتومتریست‌ها | جراحان دهان و فک و صورت | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | پزشکان طب فیزیکی و توانبخشی | پزشکان پا | متخصصان پروتز دندان | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | صحبت کردن | گوش دادن فعال | درک مطلب | نظارت | نوشتن | یادگیری فعال | علوم</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نظارت | نگارش | یادگیری فعال | علوم</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | زیست‌شناسی | آموزش و پرورش | روان‌شناسی</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | زیست‌شناسی | آموزش و پرورش | روان‌شناسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | درک شنیداری | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | مهارت انگشتان | درک نوشتاری | ثبات بازو-دست | مهارت دستی | تشخیص گفتار | وضوح گفتار | نظم‌دهی اطلاعات | بیان نوشتاری | تجسم | توجه انتخابی | دقت کنترل | تشخیص رنگ بصری | انعطاف‌پذیری دسته‌بندی | خلاقیت | روانی ایده‌ها | انعطاف‌پذیری بستار</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | مهارت انگشتان | درک کتبی | ثبات دست و بازو | مهارت دستی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | بیان کتبی | تجسم | توجه انتخابی | دقت کنترل | تشخیص رنگ بصری | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>مجاورت فیزیکی | بحث‌های حضوری با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | تعیین وظایف، اولویت‌ها و اهداف | نتایج کاری و خروجی‌های سایر کارکنان | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تماس با دیگران | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | محیط داخلی، دارای تهویه مطبوع | ایمیل | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | نامه‌ها و یادداشت‌های کتبی | قرار گرفتن در معرض بیماری یا عفونت | صرف زمان برای انجام حرکات تکراری | صرف زمان برای خم شدن یا چرخاندن بدن | صرف زمان برای نشستن | برخورد با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف مشابه | فشار زمانی | پیامد خطا | سطح رقابت</t>
+          <t>نزدیکی فیزیکی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | پیامدهای کاری و نتایج سایر کارکنان | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ارتباط با دیگران | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | نامه‌ها و یادداشت‌های کتبی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | صرف زمان برای انجام حرکات تکراری | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای نشستن | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | فشار زمانی | پیامد خطا | سطح رقابت</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>متخصصان بیهوشی | متخصصان قلب | دستیاران دندانپزشک | بهداشت‌کاران دهان و دندان | تکنسین‌های لابراتوار دندانپزشکی | دندانپزشکان، عمومی | متخصصان پوست | پزشکان طب اورژانس | تکنسین‌های تجهیزات پزشکی | چشم‌پزشکان، به جز کودکان | اپتومتریست‌ها | جراحان دهان و فک و صورت | متخصصان ارتودنسی | جراحان ارتوپد، به جز کودکان | متخصصان ارتز و پروتز | جراحان کودکان | پزشکان طب فیزیکی و توانبخشی | متخصصان پا (پودیاتریست‌ها) | دستیاران جراحی | متخصصان اورولوژی</t>
+          <t>متخصصان بیهوشی | متخصصان قلب | دستیاران دندان‌پزشکی | بهداشت‌کاران دهان و دندان | تکنسین‌های پروتز دندان | دندانپزشکان، عمومی | متخصصان پوست | پزشکان طب اورژانس | تکنسین‌های تجهیزات پزشکی | چشم‌پزشکان، به‌جز کودکان | اپتومتریست‌ها | جراحان دهان و فک و صورت | متخصصان ارتودنسی | جراحان ارتوپد، به‌جز کودکان | متخصصان ارتوپدی فنی و پروتز | جراحان کودکان | پزشکان طب فیزیکی و توانبخشی | پزشکان پا | دستیاران جراحی | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار کدگذاری روش‌های پزشکی | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | نرم‌افزار مرورگر وب | نرم‌افزار Microsoft Office | Microsoft PowerPoint</t>
+          <t>نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | نرم‌افزار مرورگر وب | نرم‌افزار Microsoft Office | Microsoft PowerPoint</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | صحبت کردن | علوم | نظارت | یادگیری فعال | نوشتن</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | شیمی | خدمات مشتری و شخصی | زبان انگلیسی | روان‌شناسی | مدیریت و اداره | آموزش و پرورش | درمان و مشاوره</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | شیمی | خدمات مشتری و شخصی | زبان انگلیسی | روان‌شناسی | مدیریت و اداره | آموزش و پرورش | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | نظم‌دهی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات بازو-دست | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | اشتراک زمانی | دقت کنترل | درک عمق | تشخیص رنگ بصری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه | دقت کنترل | درک عمق | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض بیماری یا عفونت | مجاورت فیزیکی | تماس با دیگران | برخورد با مشتریان خارجی یا عموم مردم | پیامد خطا | اهمیت دقیق یا صحیح بودن | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | بحث‌های حضوری با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | محیط داخلی، دارای تهویه مطبوع | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>دندانپزشکان، عمومی | متخصصان ارتودنسی | متخصصان پروتز دندان | جراحان دهان و فک و صورت | بهداشت‌کاران دهان و دندان | دستیاران دندانپزشک | پزشکان، سایر | جراحان، سایر | متخصصان بیهوشی | پزشکان، آسیب‌شناسان | پزشکان طب خانواده | متخصصان کودکان، عمومی | معلمان تخصص‌های سلامت، پس از متوسطه | مدیران خدمات پزشکی و سلامت | متخصصان ارتز و پروتز | دستیاران جراحی | تکنسین‌ها و کارشناسان رادیولوژی | پزشکان تشخیص یا درمان سلامت، سایر | متخصصان طب سوزنی | پزشکان طب طبیعی</t>
+          <t>دندانپزشکان، عمومی | متخصصان ارتودنسی | متخصصان پروتز دندان | جراحان دهان و فک و صورت | بهداشت‌کاران دهان و دندان | دستیاران دندان‌پزشکی | پزشکان، سایر موارد | جراحان، سایر | متخصصان بیهوشی | پزشکان، آسیب‌شناسان | پزشکان خانواده | متخصصان کودکان، عمومی | استادان تخصص‌های بهداشتی، پس از متوسطه | مدیران خدمات پزشکی و بهداشتی | متخصصان ارتوپدی فنی و پروتز | دستیاران جراحی | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | سایر متخصصان تشخیص یا درمان مراقبت‌های بهداشتی | طب‌سوزنی‌ها | پزشکان ناتوروپاتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>نرم‌افزار رژیم آلرژی‌زا | Aurora FoodPro | Axxya Systems Nutritionist Pro | BioEx Systems Nutrition Maker Plus | Compu-Cal Nutrition Assistant | Cronometer | CyberSoft NutriBase | نرم‌افزار پایگاه داده | DietMaster Systems DietMaster | ESHA Research The Food Processor | Google Drive | نرم‌افزار گرافیک | نرم‌افزار برنامه‌ریزی کتوژنیک | Lifestyles Technologies DietMaster Pro | MNT Northwest MNT Assistant | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | برنامه رژیم غذایی کم FODMAP دانشگاه موناش | Mosby's Nutritrac | MyFitnessPal | نرم‌افزار تحلیل مواد مغذی | PICS DietMate Professional | ReadyTalk | Skype | نرم‌افزار آماری | SureQuest Systems Square 1 | The Nutrition Company FoodWorks | ValuSoft MasterCook | نرم‌افزار مرورگر وب</t>
+          <t>نرم‌افزار رژیم آلرژی‌زا | Aurora FoodPro | Axxya Systems Nutritionist Pro | BioEx Systems Nutrition Maker Plus | Compu-Cal Nutrition Assistant | Cronometer | CyberSoft NutriBase | نرم‌افزار پایگاه داده | DietMaster Systems DietMaster | ESHA Research The Food Processor | Google Drive | نرم‌افزار گرافیکی | نرم‌افزار برنامه‌ریزی کتوژنیک | Lifestyles Technologies DietMaster Pro | MNT Northwest MNT Assistant | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | برنامه رژیم غذایی کم FODMAP دانشگاه موناش | Mosby's Nutritrac | MyFitnessPal | نرم‌افزار تحلیل مواد مغذی | PICS DietMate Professional | ReadyTalk | Skype | نرم‌افزار آماری | SureQuest Systems Square 1 | The Nutrition Company FoodWorks | ValuSoft MasterCook | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>صحبت کردن | تفکر انتقادی | گوش دادن فعال | درک مطلب | نوشتن | نظارت | استراتژی‌های یادگیری | یادگیری فعال | علوم | ریاضیات</t>
+          <t>سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | پزشکی و دندانپزشکی | زبان انگلیسی | درمان و مشاوره | خدمات مشتری و شخصی | روان‌شناسی | آموزش و پرورش | ریاضیات | کامپیوتر و الکترونیک | شیمی | جامعه‌شناسی و مردم‌شناسی | تولید مواد غذایی</t>
+          <t>زیست‌شناسی | پزشکی و دندان‌پزشکی | زبان انگلیسی | درمان و مشاوره | خدمات مشتری و شخصی | روان‌شناسی | آموزش و پرورش | ریاضیات | رایانه و الکترونیک | شیمی | جامعه‌شناسی و انسان‌شناسی | تولید مواد غذایی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | تشخیص گفتار | خلاقیت | دید نزدیک | استدلال ریاضی | روانی ایده‌ها | توجه انتخابی | توانایی عددی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | تشخیص گفتار | اصالت | بینایی نزدیک | استدلال ریاضی | روانی ایده‌ها | توجه انتخابی | توانایی عددی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | مکالمات تلفنی | محیط داخلی، دارای تهویه مطبوع | تماس با دیگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | برخورد با مشتریان خارجی یا عموم مردم | صرف زمان برای نشستن | قرار گرفتن در معرض بیماری یا عفونت</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای نشستن | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>پرستاران روانپزشکی پیشرفته | متخصصان آلرژی و ایمنی‌شناسی | پرستاران متخصص بالینی | تکنسین‌های رژیم غذایی | فیزیولوژیست‌های ورزشی | پزشکان طب خانواده | پزشکان داخلی عمومی | مشاوران ژنتیک | متخصصان آموزش سلامت | پزشکان طب طبیعی | متخصصان مغز و اعصاب | ماماها | پرستاران متخصص | متخصصان زنان و زایمان | کاردرمانگران | متخصصان کودکان، عمومی | داروسازان | پزشکان طب پیشگیری | روان‌پزشکان | پرستاران ثبت‌شده</t>
+          <t>پرستاران پیشرفته روانپزشکی | متخصصان آلرژی و ایمونولوژی | متخصصان پرستاری بالینی | تکنسین‌های رژیم غذایی | فیزیولوژیست‌های ورزشی | پزشکان خانواده | پزشکان داخلی عمومی | مشاوران ژنتیک | متخصصان آموزش بهداشت | پزشکان ناتوروپاتی | متخصصان مغز و اعصاب | ماماها | پرستاران متخصص | متخصصان زنان و زایمان | کاردرمانگران | متخصصان کودکان، عمومی | داروسازان | پزشکان طب پیشگیری | روان‌پزشکان | پرستاران ثبت‌شده</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Accra Med Software Filopto | AltaPoint Data Systems AltaPoint Vision | Apple Safari | Babcock Winx Pro | Compulink Business Systems Eyecare Advantage | Digital Healthcare OptoMize | First Insight E-Z Frame | First Insight MaximEyes | HealthLine Systems Eyecom | Insight Software My Vision Express | Intuit QuickBooks | MAX Systems Max-Gold7 | MediNotes Charting Plus | Microsoft Access | Microsoft Edge | Microsoft Excel | Microsoft SQL Server | Microsoft Word | Mozilla Firefox | OfficeMate Software Solutions ExamWRITER | OfficeMate Software Solutions OfficeMate | نرم‌افزار عملیاتی داده ODS | Prima Systems OPTIX | نرم‌افزار زمان‌بندی | Universal Software Solutions VersaVision | VisionScience Software Acuity Pro | نرم‌افزار مرورگر وب</t>
+          <t>Accra Med Software Filopto | AltaPoint Data Systems AltaPoint Vision | Apple Safari | Babcock Winx Pro | Compulink Business Systems Eyecare Advantage | Digital Healthcare OptoMize | First Insight E-Z Frame | First Insight MaximEyes | HealthLine Systems Eyecom | Insight Software My Vision Express | Intuit QuickBooks | MAX Systems Max-Gold7 | MediNotes Charting Plus | Microsoft Access | Microsoft Edge | Microsoft Excel | Microsoft SQL Server | Microsoft Word | Mozilla Firefox | OfficeMate Software Solutions ExamWRITER | OfficeMate Software Solutions OfficeMate | نرم‌افزار ذخیره‌سازی داده‌های عملیاتی ODS | Prima Systems OPTIX | نرم‌افزار زمان‌بندی | Universal Software Solutions VersaVision | VisionScience Software Acuity Pro | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | صحبت کردن | نوشتن | علوم | نظارت | استراتژی‌های یادگیری | یادگیری فعال | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | علوم | نظارت | راهبردهای یادگیری | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | زیست‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | آموزش و پرورش | درمان و مشاوره | روان‌شناسی | مدیریت و اداره | اقتصاد و حسابداری | فیزیک | اداری | قانون و دولت | کامپیوتر و الکترونیک | پرسنل و منابع انسانی | فروش و بازاریابی | ایمنی و امنیت عمومی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | آموزش و پرورش | درمان و مشاوره | روان‌شناسی | مدیریت و اداره | اقتصاد و حسابداری | فیزیک | اداری | قانون و دولت | رایانه و الکترونیک | پرسنل و منابع انسانی | فروش و بازاریابی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | درک شنیداری | درک نوشتاری | استدلال قیاسی | استدلال استقرایی | دید نزدیک | بیان نوشتاری | نظم‌دهی اطلاعات | انعطاف‌پذیری بستار | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | دید دور | توجه انتخابی | سرعت ادراکی | روانی ایده‌ها | تشخیص رنگ بصری | دقت کنترل | ثبات بازو-دست | مهارت دستی | اشتراک زمانی | تجسم | استدلال ریاضی</t>
+          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | بینایی دور | توجه انتخابی | سرعت ادراکی | روانی ایده‌ها | تشخیص رنگ بصری | دقت کنترل | ثبات دست و بازو | مهارت دستی | تقسیم توجه | تجسم | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای تهویه مطبوع | ایمیل | اهمیت دقیق یا صحیح بودن | تماس با دیگران | آزادی در تصمیم‌گیری | مجاورت فیزیکی | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | برخورد با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | فشار زمانی | قرار گرفتن در معرض بیماری یا عفونت | اهمیت تکرار وظایف مشابه | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن | صرف زمان برای انجام حرکات تکراری | نتایج کاری و خروجی‌های سایر کارکنان | سطح رقابت</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | اهمیت دقیق یا درست بودن | ارتباط با دیگران | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | فشار زمانی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | اهمیت تکرار وظایف یکسان | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن | صرف زمان برای انجام حرکات تکراری | پیامدهای کاری و نتایج سایر کارکنان | سطح رقابت</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیهوشی | شنوایی‌شناسان | کایروپراکتورها | متخصصان پوست | پزشکان طب اورژانس | پزشکان داخلی عمومی | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | تکنسین‌های پزشکی چشم | کارشناسان پزشکی چشم | چشم‌پزشکان، به جز کودکان | جراحان دهان و فک و صورت | جراحان ارتوپد، به جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | متخصصان پا (پودیاتریست‌ها) | متخصصان اورولوژی</t>
+          <t>متخصصان آلرژی و ایمونولوژی | متخصصان بیهوشی | شنوایی‌شناسان | کایروپراکتورها | متخصصان پوست | پزشکان طب اورژانس | پزشکان داخلی عمومی | متخصصان مغز و اعصاب | پرستاران متخصص | متخصصان زنان و زایمان | تکنسین‌های پزشکی چشم‌پزشکی | تکنولوژیست‌های پزشکی چشم‌پزشکی | چشم‌پزشکان، به‌جز کودکان | جراحان دهان و فک و صورت | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | متخصصان کودکان، عمومی | پزشکان طب فیزیکی و توانبخشی | پزشکان پا | اورولوژیست‌ها</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>سیستم‌های سوابق کامپیوتری | Epic Systems | Freedom MedTEACH | Healthprolink MedAtlas | نرم‌افزار پردازش ادعای بیمه | نرم‌افزار برچسب‌زنی | نرم‌افزار MEDITECH | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | نرم‌افزار چندوظیفه‌ای | نرم‌افزار Pyxis MedStation | نرم‌افزار ثبت سوابق | RxKinetics UD Labels for Windows | TPNassist | TTP LabTech comPOUND | نرم‌افزار مرورگر وب | نرم‌افزار پرونده الکترونیک سلامت eClinicalWorks</t>
+          <t>سیستم‌های سوابق کامپیوتری | Epic Systems | Freedom MedTEACH | Healthprolink MedAtlas | نرم‌افزار پردازش ادعای بیمه | نرم‌افزار برچسب‌زنی | نرم‌افزار MEDITECH | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | نرم‌افزار چندوظیفه‌ای | نرم‌افزار Pyxis MedStation | نرم‌افزار ثبت سوابق | RxKinetics UD Labels for Windows | TPNassist | TTP LabTech comPOUND | نرم‌افزار مرورگر وب | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>صحبت کردن | گوش دادن فعال | درک مطلب | نوشتن | تفکر انتقادی | نظارت | یادگیری فعال | علوم | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | علوم | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | ریاضیات | خدمات مشتری و شخصی | زبان انگلیسی | شیمی | زیست‌شناسی | روان‌شناسی | کامپیوتر و الکترونیک | آموزش و پرورش | اداری</t>
+          <t>پزشکی و دندان‌پزشکی | ریاضیات | خدمات مشتری و شخصی | زبان انگلیسی | شیمی | زیست‌شناسی | روان‌شناسی | رایانه و الکترونیک | آموزش و پرورش | اداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شنیداری | درک نوشتاری | حساسیت به مسئله | دید نزدیک | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | استدلال ریاضی | توانایی عددی | روانی ایده‌ها | مهارت انگشتان | توجه انتخابی | سرعت ادراکی | مهارت دستی | اشتراک زمانی | تشخیص رنگ بصری | دید دور | حافظه‌سپاری</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | بینایی نزدیک | بیان کتبی | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | استدلال ریاضی | توانایی عددی | روانی ایده‌ها | مهارت انگشتان | توجه انتخابی | سرعت ادراکی | مهارت دستی | تقسیم توجه | تشخیص رنگ بصری | بینایی دور | حفظ کردن</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>محیط داخلی، دارای تهویه مطبوع | مکالمات تلفنی | اهمیت دقیق یا صحیح بودن | بحث‌های حضوری با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تماس با دیگران | پیامد خطا | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با مشتریان خارجی یا عموم مردم | فشار زمانی | ایمیل | آزادی در تصمیم‌گیری | نتایج کاری و خروجی‌های سایر کارکنان | اهمیت تکرار وظایف مشابه | قرار گرفتن در معرض بیماری یا عفونت | صرف زمان برای ایستادن | مجاورت فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | سطح رقابت | موقعیت‌های تعارض</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | پیامد خطا | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی | ایمیل | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | صرف زمان برای ایستادن | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | سلامت و ایمنی سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | سطح رقابت | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | متخصصان آلرژی و ایمنی‌شناسی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | پرستاران متخصص بالینی | پزشکان طب اورژانس | پزشکان طب خانواده | پزشکان داخلی عمومی | پزشکان بیمارستانی | پرستاران عملی و حرفه‌ای دارای مجوز | دستیاران پزشکی | پرستاران بیهوشی | پرستاران متخصص | متخصصان زنان و زایمان | پیراپزشکان | متخصصان کودکان، عمومی | تکنسین‌های داروسازی | دستیاران پزشک | پزشکان طب پیشگیری | پرستاران ثبت‌شده</t>
+          <t>پرستاران مراقبت‌های ویژه | متخصصان آلرژی و ایمونولوژی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | متخصصان پرستاری بالینی | پزشکان طب اورژانس | پزشکان خانواده | پزشکان داخلی عمومی | پزشکان بیمارستانی | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | دستیاران پزشکی | پرستاران بیهوشی | پرستاران متخصص | متخصصان زنان و زایمان | پارامدیک‌ها | متخصصان کودکان، عمومی | تکنسین‌های داروسازی | دستیاران پزشک | پزشکان طب پیشگیری | پرستاران ثبت‌شده</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0042_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0042_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مخابرات | کامپیوتر و الکترونیک | ارتباطات و رسانه | زبان انگلیسی | مهندسی و فناوری | هنرهای تجسمی و نمایشی | خدمات مشتریان و خدمات فردی</t>
+          <t>مخابرات | رایانه و الکترونیک | ارتباطات و رسانه | زبان انگلیسی | مهندسی و فناوری | هنرهای زیبا | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | تجسم فضایی | ثبات دست و بازو | چابکی انگشتان | چابکی دستی | دقت کنترل حرکتی | هماهنگی اندام‌ها | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | استدلال ریاضی | دید دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنسین‌های صوت و تصویر | تکنسین‌های پخش | تکنسین‌های صدابرداری و مهندسی صدا | تکنسین‌های نورپردازی | تصویربرداران تلویزیون، ویدئو و سینما | تدوین‌گران فیلم و ویدئو | عکاسان | مدیران فنی و کارگردانان فنی رسانه | تهیه‌کنندگان و کارگردانان | نصابان و تعمیرکاران تجهیزات مخابراتی، به‌جز نصابان خطوط ارتباطی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | نصابان و تعمیرکاران تجهیزات رادیویی، دکل‌ها و شبکه‌های سلولی | کارشناسان پشتیبانی کاربران کامپیوتر | طراحان جلوه‌های ویژه و انیماتورها | طراحان صحنه و دکور | مدیران برنامه‌ریزی رسانه | نصابان و تعمیرکاران تجهیزات صوتی و تصویری | برق‌کاران | مهندسان تاسیسات ثابت و متصدیان دیگ‌های بخار | سایر متخصصان و فعالان حوزه رسانه و ارتباطات</t>
+          <t>تکنسین‌های تجهیزات صوتی و تصویری | تکنسین‌های پخش و اتاق فرمان | تکنسین‌های مهندسی صدا | تکنسین‌های نورپردازی | تصویربرداران تلویزیون، ویدیو و سینما | تدوین‌گران فیلم و ویدیو | عکاسان | مدیران فنی رسانه | تهیه‌کنندگان و کارگردانان | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | متخصصان پشتیبانی کاربران رایانه | پویانماها و طراحان جلوه‌های ویژه | طراحان صحنه و نمایشگاه | مدیران برنامه‌ریزی و پخش رسانه | نصاب و تعمیرکار تجهیزات صوتی و تصویری | برق‌کاران | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | سایر کارشناسان حوزه رسانه و ارتباطات</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | علوم تجربی و پایه | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | علوم | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | زیست‌شناسی | روان‌شناسی | مدیریت و امور اداری | امور اداری و دفتری | پرسنلی و منابع انسانی | آموزش و تدریس | درمان و مشاوره | بازاریابی و فروش | کامپیوتر و الکترونیک</t>
+          <t>پزشکی و دندان‌پزشکی | زبان انگلیسی | خدمات مشتری و شخصی | زیست‌شناسی | روان‌شناسی | مدیریت و اداره | اداری | پرسنل و منابع انسانی | آموزش و پرورش | درمان و مشاوره | فروش و بازاریابی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | مرتب‌سازی اطلاعات | وضوح گفتار | دید نزدیک | تشخیص گفتار | قدرت تنه | هماهنگی اندام‌ها | ثبات دست و بازو | انعطاف‌پذیری در بستار | انعطاف‌پذیری در طبقه‌بندی | توجه انتخابی | چابکی انگشتان | روانی و سیالی ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | ترتیب‌دهی اطلاعات | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | قدرت تنه | هماهنگی چند عضو | ثبات دست و بازو | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | مهارت انگشتان | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>متخصصان طب سوزنی | متخصصان آلرژی و ایمونولوژی بالینی | متخصصان بیهوشی | متخصصان قلب و عروق | متخصصان پوست، مو و زیبایی | متخصصان طب اورژانس | پزشکان عمومی و خانواده | متخصصان بیماری‌های داخلی | پزشکان طب سنتی و طبیعی | متخصصان مغز و اعصاب (نورولوژیست) | پرستاران دوره‌دیده مراقبت‌های پیشرفته | متخصصان زنان و زایمان | چشم‌پزشکان (به‌جز اطفال) | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان ارتوپدی (به‌جز اطفال) | جراحان اطفال | متخصصان کودکان و اطفال | متخصصان طب فیزیکی و توان‌بخشی | روان‌پزشکان | متخصصان کلیه و مجاری ادراری (اورولوژیست)</t>
+          <t>متخصصان و کارشناسان طب سوزنی | متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | پزشکان طب طبیعی و نتوپاتی | متخصصان مغز و اعصاب | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی، غیر از اطفال | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | روان‌پزشکان | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | سخن گفتن | شنیدن فعال | درک مطلب | یادگیری فعال | علوم تجربی و پایه | نگارش | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال | درک مطلب | یادگیری فعال | علوم | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | زیست‌شناسی | روان‌شناسی | آموزش و تدریس | مدیریت و امور اداری | پرسنلی و منابع انسانی | اقتصاد و حسابداری</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زبان انگلیسی | زیست‌شناسی | روان‌شناسی | آموزش و پرورش | مدیریت و اداره | پرسنل و منابع انسانی | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>چابکی انگشتان | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ثبات دست و بازو | دید نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | دقت کنترل حرکتی | وضوح گفتار | مرتب‌سازی اطلاعات | توجه انتخابی | چابکی دستی | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | هماهنگی اندام‌ها | انعطاف‌پذیری در بستار | بیان کتبی | تجسم فضایی | روانی و سیالی ایده‌ها | اصالت و ابتکار | تشخیص رنگ‌ها | درک عمق | سرعت ادراک | تسلط بر کار با اعداد | استدلال ریاضی</t>
+          <t>مهارت انگشتان | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ثبات دست و بازو | بینایی نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | دقت کنترل | وضوح گفتار | ترتیب‌دهی اطلاعات | توجه انتخابی | مهارت دستی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | هماهنگی چند عضو | انعطاف‌پذیری بستار | بیان کتبی | تجسم | روانی ایده‌ها | اصالت | تشخیص رنگ بصری | درک عمق | سرعت ادراکی | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>متخصصان بیهوشی | متخصصان قلب و عروق | کایروپراکتورها | دستیاران دندان‌پزشک | کارشناسان بهداشت دهان و دندان | متخصصان پوست، مو و زیبایی | متخصصان طب اورژانس | متخصصان بیماری‌های داخلی | دستیاران پزشک | چشم‌پزشکان (به‌جز اطفال) | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان دهان، فک و صورت | متخصصان ارتودنسی | جراحان ارتوپدی (به‌جز اطفال) | جراحان اطفال | متخصصان طب فیزیکی و توان‌بخشی | متخصصان طب پا (پودیاتریست‌ها) | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | دستیاران جراحی | متخصصان کلیه و مجاری ادراری (اورولوژیست)</t>
+          <t>متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | کایروپراکتورها / متخصصان درمان دستی | دستیاران دندان‌پزشک | بهداشت‌کاران دهان و دندان | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | کمک‌پزشکان و دستیاران مطب | متخصصان چشم‌پزشکی، غیر از اطفال | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان دهان، فک و صورت | متخصصان ارتودنسی | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | پزشکان متخصص پا و مچ پا | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | دستیاران جراحی | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | یادگیری فعال | نظارت | نگارش | علوم تجربی و پایه</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نظارت | نگارش | علوم</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | روان‌شناسی | آموزش و تدریس | شیمی | مدیریت و امور اداری | پرسنلی و منابع انسانی | درمان و مشاوره | ریاضیات</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی | آموزش و پرورش | شیمی | مدیریت و اداره | پرسنل و منابع انسانی | درمان و مشاوره | ریاضیات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی انگشتان | دید نزدیک | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | دقت کنترل حرکتی | درک کتبی | مرتب‌سازی اطلاعات | چابکی دستی | وضوح گفتار | تشخیص گفتار | بیان کتبی | توجه انتخابی | انعطاف‌پذیری در بستار | انعطاف‌پذیری در طبقه‌بندی | هماهنگی اندام‌ها | تشخیص رنگ‌ها | تجسم فضایی | اصالت و ابتکار | سرعت ادراک | روانی و سیالی ایده‌ها</t>
+          <t>ثبات دست و بازو | مهارت انگشتان | بینایی نزدیک | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | دقت کنترل | درک کتبی | ترتیب‌دهی اطلاعات | مهارت دستی | وضوح گفتار | تشخیص گفتار | بیان کتبی | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | هماهنگی چند عضو | تشخیص رنگ بصری | تجسم | اصالت | سرعت ادراکی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متخصصان بیهوشی | متخصصان قلب و عروق | دستیاران دندان‌پزشک | کارشناسان بهداشت دهان و دندان | دندان‌پزشکان عمومی | متخصصان پوست، مو و زیبایی | متخصصان طب اورژانس | متخصصان بیماری‌های داخلی | متخصصان مغز و اعصاب (نورولوژیست) | متخصصان زنان و زایمان | چشم‌پزشکان (به‌جز اطفال) | بینایی‌سنج‌ها (اپتومتریست‌ها) | متخصصان ارتودنسی | جراحان ارتوپدی (به‌جز اطفال) | جراحان اطفال | متخصصان طب فیزیکی و توان‌بخشی | متخصصان طب پا (پودیاتریست‌ها) | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | دستیاران جراحی | متخصصان کلیه و مجاری ادراری (اورولوژیست)</t>
+          <t>متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | دستیاران دندان‌پزشک | بهداشت‌کاران دهان و دندان | دندان‌پزشکان عمومی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | متخصصان مغز و اعصاب | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی، غیر از اطفال | بینایی‌سنج‌ها (اپتومتریست‌ها) | متخصصان ارتودنسی | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | پزشکان متخصص پا و مچ پا | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | دستیاران جراحی | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب | یادگیری فعال | نگارش | علوم تجربی و پایه | راهبردهای یادگیری</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | یادگیری فعال | نگارش | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | زیست‌شناسی | کامپیوتر و الکترونیک | ریاضیات | مدیریت و امور اداری | آموزش و تدریس | فیزیک | مهندسی و فناوری</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زبان انگلیسی | زیست‌شناسی | رایانه و الکترونیک | ریاضیات | مدیریت و اداره | آموزش و پرورش | فیزیک | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ثبات دست و بازو | چابکی انگشتان | دید نزدیک | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | چابکی دستی | انعطاف‌پذیری در طبقه‌بندی | توجه انتخابی | دقت کنترل حرکتی | روانی و سیالی ایده‌ها | تجسم فضایی | دید دور | تقسیم توجه | اصالت و ابتکار</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ثبات دست و بازو | مهارت انگشتان | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | مهارت دستی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | دقت کنترل | روانی ایده‌ها | تجسم | بینایی دور | تقسیم توجه | اصالت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمونولوژی بالینی | متخصصان قلب و عروق | کایروپراکتورها | دستیاران دندان‌پزشک | کارشناسان بهداشت دهان و دندان | دندان‌پزشکان عمومی | متخصصان پوست، مو و زیبایی | متخصصان طب اورژانس | متخصصان بیماری‌های داخلی | متخصصان مغز و اعصاب (نورولوژیست) | متخصصان زنان و زایمان | چشم‌پزشکان (به‌جز اطفال) | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان دهان، فک و صورت | جراحان ارتوپدی (به‌جز اطفال) | جراحان اطفال | متخصصان طب فیزیکی و توان‌بخشی | متخصصان طب پا (پودیاتریست‌ها) | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | متخصصان کلیه و مجاری ادراری (اورولوژیست)</t>
+          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیماری‌های قلب و عروق | کایروپراکتورها / متخصصان درمان دستی | دستیاران دندان‌پزشک | بهداشت‌کاران دهان و دندان | دندان‌پزشکان عمومی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | متخصصان مغز و اعصاب | متخصصان زنان و زایمان | متخصصان چشم‌پزشکی، غیر از اطفال | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان دهان، فک و صورت | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | پزشکان متخصص پا و مچ پا | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نظارت | نگارش | یادگیری فعال | علوم تجربی و پایه</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نظارت | نگارش | یادگیری فعال | علوم</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | زبان انگلیسی | زیست‌شناسی | آموزش و تدریس | روان‌شناسی</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | زیست‌شناسی | آموزش و پرورش | روان‌شناسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | چابکی انگشتان | درک کتبی | ثبات دست و بازو | چابکی دستی | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | بیان کتبی | تجسم فضایی | توجه انتخابی | دقت کنترل حرکتی | تشخیص رنگ‌ها | انعطاف‌پذیری در طبقه‌بندی | اصالت و ابتکار | روانی و سیالی ایده‌ها | انعطاف‌پذیری در بستار</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | مهارت انگشتان | درک کتبی | ثبات دست و بازو | مهارت دستی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | بیان کتبی | تجسم | توجه انتخابی | دقت کنترل | تشخیص رنگ بصری | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>متخصصان بیهوشی | متخصصان قلب و عروق | دستیاران دندان‌پزشک | کارشناسان بهداشت دهان و دندان | تکنسین‌های پروتزهای دندانی (لابراتوار دندان‌سازی) | دندان‌پزشکان عمومی | متخصصان پوست، مو و زیبایی | متخصصان طب اورژانس | تکنسین‌های ساخت وسایل و پروتزهای ارتوپدی و پزشکی | چشم‌پزشکان (به‌جز اطفال) | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان دهان، فک و صورت | متخصصان ارتودنسی | جراحان ارتوپدی (به‌جز اطفال) | متخصصان ساخت ارتوز و پروتز (اعضای مصنوعی) | جراحان اطفال | متخصصان طب فیزیکی و توان‌بخشی | متخصصان طب پا (پودیاتریست‌ها) | دستیاران جراحی | متخصصان کلیه و مجاری ادراری (اورولوژیست)</t>
+          <t>متخصصان بیهوشی | متخصصان بیماری‌های قلب و عروق | دستیاران دندان‌پزشک | بهداشت‌کاران دهان و دندان | تکنسین‌های پروتزهای دندانی و لابراتوار دندانسازی | دندان‌پزشکان عمومی | متخصصان پوست و مو | پزشکان طب اورژانس | تکنسین‌های ساخت پروتز و اعضای مصنوعی پزشکی | متخصصان چشم‌پزشکی، غیر از اطفال | بینایی‌سنج‌ها (اپتومتریست‌ها) | جراحان دهان، فک و صورت | متخصصان ارتودنسی | جراحان ارتوپدی، غیر از اطفال | ارتوپدهای فنی و سازندگان اعضای مصنوعی | جراحان اطفال | متخصصان طب فیزیکی و توانبخشی | پزشکان متخصص پا و مچ پا | دستیاران جراحی | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم تجربی و پایه | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | شیمی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | روان‌شناسی | مدیریت و امور اداری | آموزش و تدریس | درمان و مشاوره</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | شیمی | خدمات مشتری و شخصی | زبان انگلیسی | روان‌شناسی | مدیریت و اداره | آموزش و پرورش | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | چابکی انگشتان | ثبات دست و بازو | چابکی دستی | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | تجسم فضایی | تقسیم توجه | دقت کنترل حرکتی | درک عمق | تشخیص رنگ‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه | دقت کنترل | درک عمق | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>دندان‌پزشکان عمومی | متخصصان ارتودنسی | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | جراحان دهان، فک و صورت | کارشناسان بهداشت دهان و دندان | دستیاران دندان‌پزشک | سایر پزشکان متخصص | سایر جراحان متخصص | متخصصان بیهوشی | پزشکان متخصص پاتولوژی (آسیب‌شناسی) | پزشکان عمومی و خانواده | متخصصان کودکان و اطفال | اساتید و مربیان دانشگاهی رشته‌های علوم پزشکی | مدیران خدمات بهداشتی و درمانی | متخصصان ساخت ارتوز و پروتز (اعضای مصنوعی) | دستیاران جراحی | کارشناسان و تکنسین‌های رادیولوژی | سایر متخصصان تشخیص و درمان حوزه سلامت | متخصصان طب سوزنی | پزشکان طب سنتی و طبیعی</t>
+          <t>دندان‌پزشکان عمومی | متخصصان ارتودنسی | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | جراحان دهان، فک و صورت | بهداشت‌کاران دهان و دندان | دستیاران دندان‌پزشک | پزشکان، سایر تخصص‌ها | سایر جراحان | متخصصان بیهوشی | پزشکان متخصص پاتولوژی | پزشکان عمومی و خانواده | متخصصان عمومی کودکان | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | مدیران خدمات درمانی و بهداشتی | ارتوپدهای فنی و سازندگان اعضای مصنوعی | دستیاران جراحی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | سایر متخصصان تشخیص و درمان حوزه سلامت | متخصصان و کارشناسان طب سوزنی | پزشکان طب طبیعی و نتوپاتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | تفکر انتقادی | شنیدن فعال | درک مطلب | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال | علوم تجربی و پایه | ریاضیات</t>
+          <t>سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | پزشکی و دندان‌پزشکی | زبان انگلیسی | درمان و مشاوره | خدمات مشتریان و خدمات فردی | روان‌شناسی | آموزش و تدریس | ریاضیات | کامپیوتر و الکترونیک | شیمی | جامعه‌شناسی و مردم‌شناسی | صنایع و تولید مواد غذایی</t>
+          <t>زیست‌شناسی | پزشکی و دندان‌پزشکی | زبان انگلیسی | درمان و مشاوره | خدمات مشتری و شخصی | روان‌شناسی | آموزش و پرورش | ریاضیات | رایانه و الکترونیک | شیمی | جامعه‌شناسی و انسان‌شناسی | تولید مواد غذایی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | تشخیص گفتار | اصالت و ابتکار | دید نزدیک | استدلال ریاضی | روانی و سیالی ایده‌ها | توجه انتخابی | تسلط بر کار با اعداد</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | تشخیص گفتار | اصالت | بینایی نزدیک | استدلال ریاضی | روانی ایده‌ها | توجه انتخابی | توانایی عددی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>پرستاران دوره‌دیده مراقبت‌های روان‌پزشکی | متخصصان آلرژی و ایمونولوژی بالینی | پرستاران بالینی متخصص | تکنسین‌ها و کاردان‌های تغذیه | فیزیولوژیست‌های ورزشی | پزشکان عمومی و خانواده | متخصصان بیماری‌های داخلی | مشاوران ژنتیک | کارشناسان آموزش و ارتقای سلامت | پزشکان طب سنتی و طبیعی | متخصصان مغز و اعصاب (نورولوژیست) | ماماها | پرستاران دوره‌دیده مراقبت‌های پیشرفته | متخصصان زنان و زایمان | کاردرمانگران | متخصصان کودکان و اطفال | داروسازان | متخصصان طب پیشگیری و پزشکی اجتماعی | روان‌پزشکان | کارشناسان پرستاری (پرستاران رسمی)</t>
+          <t>پرستاران تخصصی روانپزشکی | متخصصان آلرژی و ایمنی‌شناسی | پرستاران متخصص بالینی | کاردان‌ها و تکنسین‌های تغذیه و رژیم‌درمانی | فیزیولوژیست‌های ورزشی | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | مشاوران ژنتیک | کارشناسان آموزش بهداشت و ارتقای سلامت | پزشکان طب طبیعی و نتوپاتی | متخصصان مغز و اعصاب | ماماهای پرستار | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | کاردرمانگران | متخصصان عمومی کودکان | داروسازان | متخصصان پزشکی اجتماعی و طب پیشگیری | روان‌پزشکان | پرستاران</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | نگارش | علوم تجربی و پایه | نظارت | راهبردهای یادگیری | یادگیری فعال | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | علوم | نظارت | راهبردهای یادگیری | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | ریاضیات | آموزش و تدریس | درمان و مشاوره | روان‌شناسی | مدیریت و امور اداری | اقتصاد و حسابداری | فیزیک | امور اداری و دفتری | حقوق و مقررات دولتی | کامپیوتر و الکترونیک | پرسنلی و منابع انسانی | بازاریابی و فروش | ایمنی و امنیت عمومی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | آموزش و پرورش | درمان و مشاوره | روان‌شناسی | مدیریت و اداره | اقتصاد و حسابداری | فیزیک | اداری | قانون و دولت | رایانه و الکترونیک | پرسنل و منابع انسانی | فروش و بازاریابی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | بیان کتبی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در بستار | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری در طبقه‌بندی | چابکی انگشتان | دید دور | توجه انتخابی | سرعت ادراک | روانی و سیالی ایده‌ها | تشخیص رنگ‌ها | دقت کنترل حرکتی | ثبات دست و بازو | چابکی دستی | تقسیم توجه | تجسم فضایی | استدلال ریاضی</t>
+          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | بیان کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | بینایی دور | توجه انتخابی | سرعت ادراکی | روانی ایده‌ها | تشخیص رنگ بصری | دقت کنترل | ثبات دست و بازو | مهارت دستی | تقسیم توجه | تجسم | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمونولوژی بالینی | متخصصان بیهوشی | شنوایی‌شناسان (ادیولوژیست‌ها) | کایروپراکتورها | متخصصان پوست، مو و زیبایی | متخصصان طب اورژانس | متخصصان بیماری‌های داخلی | متخصصان مغز و اعصاب (نورولوژیست) | پرستاران دوره‌دیده مراقبت‌های پیشرفته | متخصصان زنان و زایمان | تکنسین‌های چشم‌پزشکی | کارشناسان فناوری‌های چشمی و بینایی‌سنجی | چشم‌پزشکان (به‌جز اطفال) | جراحان دهان، فک و صورت | جراحان ارتوپدی (به‌جز اطفال) | جراحان اطفال | متخصصان کودکان و اطفال | متخصصان طب فیزیکی و توان‌بخشی | متخصصان طب پا (پودیاتریست‌ها) | متخصصان کلیه و مجاری ادراری (اورولوژیست)</t>
+          <t>متخصصان آلرژی و ایمنی‌شناسی | متخصصان بیهوشی | شنوایی‌شناسان | کایروپراکتورها / متخصصان درمان دستی | متخصصان پوست و مو | پزشکان طب اورژانس | پزشکان متخصص بیماری‌های داخلی | متخصصان مغز و اعصاب | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | تکنسین‌های مراقبت‌های چشمی | کارشناسان فناوری پزشکی چشم | متخصصان چشم‌پزشکی، غیر از اطفال | جراحان دهان، فک و صورت | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | پزشکان متخصص پا و مچ پا | متخصصان اورولوژی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | علوم تجربی و پایه | ریاضیات | راهبردهای یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | علوم | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | ریاضیات | خدمات مشتریان و خدمات فردی | زبان انگلیسی | شیمی | زیست‌شناسی | روان‌شناسی | کامپیوتر و الکترونیک | آموزش و تدریس | امور اداری و دفتری</t>
+          <t>پزشکی و دندان‌پزشکی | ریاضیات | خدمات مشتری و شخصی | زبان انگلیسی | شیمی | زیست‌شناسی | روان‌شناسی | رایانه و الکترونیک | آموزش و پرورش | اداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | دید نزدیک | بیان کتبی | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | استدلال ریاضی | تسلط بر کار با اعداد | روانی و سیالی ایده‌ها | چابکی انگشتان | توجه انتخابی | سرعت ادراک | چابکی دستی | تقسیم توجه | تشخیص رنگ‌ها | دید دور | حافظه و به‌خاطرسپاری</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | بینایی نزدیک | بیان کتبی | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | استدلال ریاضی | توانایی عددی | روانی ایده‌ها | مهارت انگشتان | توجه انتخابی | سرعت ادراکی | مهارت دستی | تقسیم توجه | تشخیص رنگ بصری | بینایی دور | حفظ کردن</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>پرستاران بخش‌های مراقبت ویژه | متخصصان آلرژی و ایمونولوژی بالینی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | پرستاران بالینی متخصص | متخصصان طب اورژانس | پزشکان عمومی و خانواده | متخصصان بیماری‌های داخلی | پزشکان مقیم بیمارستان | بهیاران و کمک‌پرستاران دارای مجوز | دستیاران پزشک | متخصصان بیهوشی پرستاری (هوشبری) | پرستاران دوره‌دیده مراقبت‌های پیشرفته | متخصصان زنان و زایمان | تکنسین‌های فوریت‌های پزشکی (اورژانس) | متخصصان کودکان و اطفال | تکنسین‌های دارویی (نسخه‌پیچ‌ها) | دستیاران بالینی پزشک | متخصصان طب پیشگیری و پزشکی اجتماعی | کارشناسان پرستاری (پرستاران رسمی)</t>
+          <t>پرستاران مراقبت‌های حاد | متخصصان آلرژی و ایمنی‌شناسی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | پرستاران متخصص بالینی | پزشکان طب اورژانس | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | پزشکان مقیم بیمارستان | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پزشکان و دستیاران مطب | پرستاران بیهوشی | پرستاران بالینی پیشرفته | متخصصان زنان و زایمان | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | متخصصان عمومی کودکان | تکنسین‌های داروخانه (نسخه‌پیچ‌ها) | دستیاران پزشک | متخصصان پزشکی اجتماعی و طب پیشگیری | پرستاران</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
